--- a/backend/nhap_excel/mau_excel/mau_nhap_sinh_vien.xlsx
+++ b/backend/nhap_excel/mau_excel/mau_nhap_sinh_vien.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dữ liệu" sheetId="1" r:id="Ree31719fb6b04c36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ví dụ" sheetId="2" r:id="R301a2199d9c54a04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="3" r:id="Rde944ab9cc134e68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục" sheetId="4" r:id="R1b8d658479bc44a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hệ thống" sheetId="5" r:id="R144d35dbf3fb48cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dữ liệu" sheetId="1" r:id="Rd3dcb75f3bbd4007"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ví dụ" sheetId="2" r:id="R674365c95e9c4aeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="3" r:id="R969e23b50e4f4db5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục" sheetId="4" r:id="R10f9b665e4dd4f46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hệ thống" sheetId="5" r:id="R35ef582b5c934c02"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="230">
+  <x:cellXfs count="240">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -872,6 +872,36 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1095,800 +1125,800 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="127"/>
-      <x:c r="C4" s="100"/>
+      <x:c r="C4" s="127"/>
       <x:c r="D4" s="127"/>
       <x:c r="E4" s="127"/>
       <x:c r="F4" s="127"/>
       <x:c r="G4" s="119"/>
-      <x:c r="H4" s="100"/>
+      <x:c r="H4" s="127"/>
       <x:c r="I4" s="127"/>
       <x:c r="J4" s="127"/>
-      <x:c r="K4" s="100"/>
-      <x:c r="L4" s="101"/>
+      <x:c r="K4" s="127"/>
+      <x:c r="L4" s="230"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="112" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="128"/>
-      <x:c r="C5" s="68"/>
+      <x:c r="C5" s="128"/>
       <x:c r="D5" s="128"/>
       <x:c r="E5" s="128"/>
       <x:c r="F5" s="128"/>
       <x:c r="G5" s="120"/>
-      <x:c r="H5" s="68"/>
+      <x:c r="H5" s="128"/>
       <x:c r="I5" s="128"/>
       <x:c r="J5" s="128"/>
-      <x:c r="K5" s="68"/>
-      <x:c r="L5" s="69"/>
+      <x:c r="K5" s="128"/>
+      <x:c r="L5" s="231"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="113" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="129"/>
-      <x:c r="C6" s="106"/>
+      <x:c r="C6" s="129"/>
       <x:c r="D6" s="129"/>
       <x:c r="E6" s="129"/>
       <x:c r="F6" s="129"/>
       <x:c r="G6" s="121"/>
-      <x:c r="H6" s="106"/>
+      <x:c r="H6" s="129"/>
       <x:c r="I6" s="129"/>
       <x:c r="J6" s="129"/>
-      <x:c r="K6" s="106"/>
-      <x:c r="L6" s="107"/>
+      <x:c r="K6" s="129"/>
+      <x:c r="L6" s="232"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="112" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="128"/>
-      <x:c r="C7" s="68"/>
+      <x:c r="C7" s="128"/>
       <x:c r="D7" s="128"/>
       <x:c r="E7" s="128"/>
       <x:c r="F7" s="128"/>
       <x:c r="G7" s="120"/>
-      <x:c r="H7" s="68"/>
+      <x:c r="H7" s="128"/>
       <x:c r="I7" s="128"/>
       <x:c r="J7" s="128"/>
-      <x:c r="K7" s="68"/>
-      <x:c r="L7" s="69"/>
+      <x:c r="K7" s="128"/>
+      <x:c r="L7" s="231"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="113" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="129"/>
-      <x:c r="C8" s="106"/>
+      <x:c r="C8" s="129"/>
       <x:c r="D8" s="129"/>
       <x:c r="E8" s="129"/>
       <x:c r="F8" s="129"/>
       <x:c r="G8" s="121"/>
-      <x:c r="H8" s="106"/>
+      <x:c r="H8" s="129"/>
       <x:c r="I8" s="129"/>
       <x:c r="J8" s="129"/>
-      <x:c r="K8" s="106"/>
-      <x:c r="L8" s="107"/>
+      <x:c r="K8" s="129"/>
+      <x:c r="L8" s="232"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="112" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="128"/>
-      <x:c r="C9" s="68"/>
+      <x:c r="C9" s="128"/>
       <x:c r="D9" s="128"/>
       <x:c r="E9" s="128"/>
       <x:c r="F9" s="128"/>
       <x:c r="G9" s="120"/>
-      <x:c r="H9" s="68"/>
+      <x:c r="H9" s="128"/>
       <x:c r="I9" s="128"/>
       <x:c r="J9" s="128"/>
-      <x:c r="K9" s="68"/>
-      <x:c r="L9" s="69"/>
+      <x:c r="K9" s="128"/>
+      <x:c r="L9" s="231"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="113" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="129"/>
-      <x:c r="C10" s="106"/>
+      <x:c r="C10" s="129"/>
       <x:c r="D10" s="129"/>
       <x:c r="E10" s="129"/>
       <x:c r="F10" s="129"/>
       <x:c r="G10" s="121"/>
-      <x:c r="H10" s="106"/>
+      <x:c r="H10" s="129"/>
       <x:c r="I10" s="129"/>
       <x:c r="J10" s="129"/>
-      <x:c r="K10" s="106"/>
-      <x:c r="L10" s="107"/>
+      <x:c r="K10" s="129"/>
+      <x:c r="L10" s="232"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="112" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="128"/>
-      <x:c r="C11" s="68"/>
+      <x:c r="C11" s="128"/>
       <x:c r="D11" s="128"/>
       <x:c r="E11" s="128"/>
       <x:c r="F11" s="128"/>
       <x:c r="G11" s="120"/>
-      <x:c r="H11" s="68"/>
+      <x:c r="H11" s="128"/>
       <x:c r="I11" s="128"/>
       <x:c r="J11" s="128"/>
-      <x:c r="K11" s="68"/>
-      <x:c r="L11" s="69"/>
+      <x:c r="K11" s="128"/>
+      <x:c r="L11" s="231"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="113" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="129"/>
-      <x:c r="C12" s="106"/>
+      <x:c r="C12" s="129"/>
       <x:c r="D12" s="129"/>
       <x:c r="E12" s="129"/>
       <x:c r="F12" s="129"/>
       <x:c r="G12" s="121"/>
-      <x:c r="H12" s="106"/>
+      <x:c r="H12" s="129"/>
       <x:c r="I12" s="129"/>
       <x:c r="J12" s="129"/>
-      <x:c r="K12" s="106"/>
-      <x:c r="L12" s="107"/>
+      <x:c r="K12" s="129"/>
+      <x:c r="L12" s="232"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="112" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="128"/>
-      <x:c r="C13" s="68"/>
+      <x:c r="C13" s="128"/>
       <x:c r="D13" s="128"/>
       <x:c r="E13" s="128"/>
       <x:c r="F13" s="128"/>
       <x:c r="G13" s="120"/>
-      <x:c r="H13" s="68"/>
+      <x:c r="H13" s="128"/>
       <x:c r="I13" s="128"/>
       <x:c r="J13" s="128"/>
-      <x:c r="K13" s="68"/>
-      <x:c r="L13" s="69"/>
+      <x:c r="K13" s="128"/>
+      <x:c r="L13" s="231"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="113" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="129"/>
-      <x:c r="C14" s="106"/>
+      <x:c r="C14" s="129"/>
       <x:c r="D14" s="129"/>
       <x:c r="E14" s="129"/>
       <x:c r="F14" s="129"/>
       <x:c r="G14" s="121"/>
-      <x:c r="H14" s="106"/>
+      <x:c r="H14" s="129"/>
       <x:c r="I14" s="129"/>
       <x:c r="J14" s="129"/>
-      <x:c r="K14" s="106"/>
-      <x:c r="L14" s="107"/>
+      <x:c r="K14" s="129"/>
+      <x:c r="L14" s="232"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="112" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="128"/>
-      <x:c r="C15" s="68"/>
+      <x:c r="C15" s="128"/>
       <x:c r="D15" s="128"/>
       <x:c r="E15" s="128"/>
       <x:c r="F15" s="128"/>
       <x:c r="G15" s="120"/>
-      <x:c r="H15" s="68"/>
+      <x:c r="H15" s="128"/>
       <x:c r="I15" s="128"/>
       <x:c r="J15" s="128"/>
-      <x:c r="K15" s="68"/>
-      <x:c r="L15" s="69"/>
+      <x:c r="K15" s="128"/>
+      <x:c r="L15" s="231"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="113" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="129"/>
-      <x:c r="C16" s="106"/>
+      <x:c r="C16" s="129"/>
       <x:c r="D16" s="129"/>
       <x:c r="E16" s="129"/>
       <x:c r="F16" s="129"/>
       <x:c r="G16" s="121"/>
-      <x:c r="H16" s="106"/>
+      <x:c r="H16" s="129"/>
       <x:c r="I16" s="129"/>
       <x:c r="J16" s="129"/>
-      <x:c r="K16" s="106"/>
-      <x:c r="L16" s="107"/>
+      <x:c r="K16" s="129"/>
+      <x:c r="L16" s="232"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="112" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="128"/>
-      <x:c r="C17" s="68"/>
+      <x:c r="C17" s="128"/>
       <x:c r="D17" s="128"/>
       <x:c r="E17" s="128"/>
       <x:c r="F17" s="128"/>
       <x:c r="G17" s="120"/>
-      <x:c r="H17" s="68"/>
+      <x:c r="H17" s="128"/>
       <x:c r="I17" s="128"/>
       <x:c r="J17" s="128"/>
-      <x:c r="K17" s="68"/>
-      <x:c r="L17" s="69"/>
+      <x:c r="K17" s="128"/>
+      <x:c r="L17" s="231"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="113" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="129"/>
-      <x:c r="C18" s="106"/>
+      <x:c r="C18" s="129"/>
       <x:c r="D18" s="129"/>
       <x:c r="E18" s="129"/>
       <x:c r="F18" s="129"/>
       <x:c r="G18" s="121"/>
-      <x:c r="H18" s="106"/>
+      <x:c r="H18" s="129"/>
       <x:c r="I18" s="129"/>
       <x:c r="J18" s="129"/>
-      <x:c r="K18" s="106"/>
-      <x:c r="L18" s="107"/>
+      <x:c r="K18" s="129"/>
+      <x:c r="L18" s="232"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="112" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="128"/>
-      <x:c r="C19" s="68"/>
+      <x:c r="C19" s="128"/>
       <x:c r="D19" s="128"/>
       <x:c r="E19" s="128"/>
       <x:c r="F19" s="128"/>
       <x:c r="G19" s="120"/>
-      <x:c r="H19" s="68"/>
+      <x:c r="H19" s="128"/>
       <x:c r="I19" s="128"/>
       <x:c r="J19" s="128"/>
-      <x:c r="K19" s="68"/>
-      <x:c r="L19" s="69"/>
+      <x:c r="K19" s="128"/>
+      <x:c r="L19" s="231"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="113" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="129"/>
-      <x:c r="C20" s="106"/>
+      <x:c r="C20" s="129"/>
       <x:c r="D20" s="129"/>
       <x:c r="E20" s="129"/>
       <x:c r="F20" s="129"/>
       <x:c r="G20" s="121"/>
-      <x:c r="H20" s="106"/>
+      <x:c r="H20" s="129"/>
       <x:c r="I20" s="129"/>
       <x:c r="J20" s="129"/>
-      <x:c r="K20" s="106"/>
-      <x:c r="L20" s="107"/>
+      <x:c r="K20" s="129"/>
+      <x:c r="L20" s="232"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="112" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="128"/>
-      <x:c r="C21" s="68"/>
+      <x:c r="C21" s="128"/>
       <x:c r="D21" s="128"/>
       <x:c r="E21" s="128"/>
       <x:c r="F21" s="128"/>
       <x:c r="G21" s="120"/>
-      <x:c r="H21" s="68"/>
+      <x:c r="H21" s="128"/>
       <x:c r="I21" s="128"/>
       <x:c r="J21" s="128"/>
-      <x:c r="K21" s="68"/>
-      <x:c r="L21" s="69"/>
+      <x:c r="K21" s="128"/>
+      <x:c r="L21" s="231"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="113" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="129"/>
-      <x:c r="C22" s="106"/>
+      <x:c r="C22" s="129"/>
       <x:c r="D22" s="129"/>
       <x:c r="E22" s="129"/>
       <x:c r="F22" s="129"/>
       <x:c r="G22" s="121"/>
-      <x:c r="H22" s="106"/>
+      <x:c r="H22" s="129"/>
       <x:c r="I22" s="129"/>
       <x:c r="J22" s="129"/>
-      <x:c r="K22" s="106"/>
-      <x:c r="L22" s="107"/>
+      <x:c r="K22" s="129"/>
+      <x:c r="L22" s="232"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="112" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="128"/>
-      <x:c r="C23" s="68"/>
+      <x:c r="C23" s="128"/>
       <x:c r="D23" s="128"/>
       <x:c r="E23" s="128"/>
       <x:c r="F23" s="128"/>
       <x:c r="G23" s="120"/>
-      <x:c r="H23" s="68"/>
+      <x:c r="H23" s="128"/>
       <x:c r="I23" s="128"/>
       <x:c r="J23" s="128"/>
-      <x:c r="K23" s="68"/>
-      <x:c r="L23" s="69"/>
+      <x:c r="K23" s="128"/>
+      <x:c r="L23" s="231"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="113" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="129"/>
-      <x:c r="C24" s="106"/>
+      <x:c r="C24" s="129"/>
       <x:c r="D24" s="129"/>
       <x:c r="E24" s="129"/>
       <x:c r="F24" s="129"/>
       <x:c r="G24" s="121"/>
-      <x:c r="H24" s="106"/>
+      <x:c r="H24" s="129"/>
       <x:c r="I24" s="129"/>
       <x:c r="J24" s="129"/>
-      <x:c r="K24" s="106"/>
-      <x:c r="L24" s="107"/>
+      <x:c r="K24" s="129"/>
+      <x:c r="L24" s="232"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="112" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="128"/>
-      <x:c r="C25" s="68"/>
+      <x:c r="C25" s="128"/>
       <x:c r="D25" s="128"/>
       <x:c r="E25" s="128"/>
       <x:c r="F25" s="128"/>
       <x:c r="G25" s="120"/>
-      <x:c r="H25" s="68"/>
+      <x:c r="H25" s="128"/>
       <x:c r="I25" s="128"/>
       <x:c r="J25" s="128"/>
-      <x:c r="K25" s="68"/>
-      <x:c r="L25" s="69"/>
+      <x:c r="K25" s="128"/>
+      <x:c r="L25" s="231"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="113" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="129"/>
-      <x:c r="C26" s="106"/>
+      <x:c r="C26" s="129"/>
       <x:c r="D26" s="129"/>
       <x:c r="E26" s="129"/>
       <x:c r="F26" s="129"/>
       <x:c r="G26" s="121"/>
-      <x:c r="H26" s="106"/>
+      <x:c r="H26" s="129"/>
       <x:c r="I26" s="129"/>
       <x:c r="J26" s="129"/>
-      <x:c r="K26" s="106"/>
-      <x:c r="L26" s="107"/>
+      <x:c r="K26" s="129"/>
+      <x:c r="L26" s="232"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="112" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="128"/>
-      <x:c r="C27" s="68"/>
+      <x:c r="C27" s="128"/>
       <x:c r="D27" s="128"/>
       <x:c r="E27" s="128"/>
       <x:c r="F27" s="128"/>
       <x:c r="G27" s="120"/>
-      <x:c r="H27" s="68"/>
+      <x:c r="H27" s="128"/>
       <x:c r="I27" s="128"/>
       <x:c r="J27" s="128"/>
-      <x:c r="K27" s="68"/>
-      <x:c r="L27" s="69"/>
+      <x:c r="K27" s="128"/>
+      <x:c r="L27" s="231"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="113" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="129"/>
-      <x:c r="C28" s="106"/>
+      <x:c r="C28" s="129"/>
       <x:c r="D28" s="129"/>
       <x:c r="E28" s="129"/>
       <x:c r="F28" s="129"/>
       <x:c r="G28" s="121"/>
-      <x:c r="H28" s="106"/>
+      <x:c r="H28" s="129"/>
       <x:c r="I28" s="129"/>
       <x:c r="J28" s="129"/>
-      <x:c r="K28" s="106"/>
-      <x:c r="L28" s="107"/>
+      <x:c r="K28" s="129"/>
+      <x:c r="L28" s="232"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="112" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="128"/>
-      <x:c r="C29" s="68"/>
+      <x:c r="C29" s="128"/>
       <x:c r="D29" s="128"/>
       <x:c r="E29" s="128"/>
       <x:c r="F29" s="128"/>
       <x:c r="G29" s="120"/>
-      <x:c r="H29" s="68"/>
+      <x:c r="H29" s="128"/>
       <x:c r="I29" s="128"/>
       <x:c r="J29" s="128"/>
-      <x:c r="K29" s="68"/>
-      <x:c r="L29" s="69"/>
+      <x:c r="K29" s="128"/>
+      <x:c r="L29" s="231"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="113" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="129"/>
-      <x:c r="C30" s="106"/>
+      <x:c r="C30" s="129"/>
       <x:c r="D30" s="129"/>
       <x:c r="E30" s="129"/>
       <x:c r="F30" s="129"/>
       <x:c r="G30" s="121"/>
-      <x:c r="H30" s="106"/>
+      <x:c r="H30" s="129"/>
       <x:c r="I30" s="129"/>
       <x:c r="J30" s="129"/>
-      <x:c r="K30" s="106"/>
-      <x:c r="L30" s="107"/>
+      <x:c r="K30" s="129"/>
+      <x:c r="L30" s="232"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="112" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="128"/>
-      <x:c r="C31" s="68"/>
+      <x:c r="C31" s="128"/>
       <x:c r="D31" s="128"/>
       <x:c r="E31" s="128"/>
       <x:c r="F31" s="128"/>
       <x:c r="G31" s="120"/>
-      <x:c r="H31" s="68"/>
+      <x:c r="H31" s="128"/>
       <x:c r="I31" s="128"/>
       <x:c r="J31" s="128"/>
-      <x:c r="K31" s="68"/>
-      <x:c r="L31" s="69"/>
+      <x:c r="K31" s="128"/>
+      <x:c r="L31" s="231"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="113" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="129"/>
-      <x:c r="C32" s="106"/>
+      <x:c r="C32" s="129"/>
       <x:c r="D32" s="129"/>
       <x:c r="E32" s="129"/>
       <x:c r="F32" s="129"/>
       <x:c r="G32" s="121"/>
-      <x:c r="H32" s="106"/>
+      <x:c r="H32" s="129"/>
       <x:c r="I32" s="129"/>
       <x:c r="J32" s="129"/>
-      <x:c r="K32" s="106"/>
-      <x:c r="L32" s="107"/>
+      <x:c r="K32" s="129"/>
+      <x:c r="L32" s="232"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="112" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="128"/>
-      <x:c r="C33" s="68"/>
+      <x:c r="C33" s="128"/>
       <x:c r="D33" s="128"/>
       <x:c r="E33" s="128"/>
       <x:c r="F33" s="128"/>
       <x:c r="G33" s="120"/>
-      <x:c r="H33" s="68"/>
+      <x:c r="H33" s="128"/>
       <x:c r="I33" s="128"/>
       <x:c r="J33" s="128"/>
-      <x:c r="K33" s="68"/>
-      <x:c r="L33" s="69"/>
+      <x:c r="K33" s="128"/>
+      <x:c r="L33" s="231"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="113" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="129"/>
-      <x:c r="C34" s="106"/>
+      <x:c r="C34" s="129"/>
       <x:c r="D34" s="129"/>
       <x:c r="E34" s="129"/>
       <x:c r="F34" s="129"/>
       <x:c r="G34" s="121"/>
-      <x:c r="H34" s="106"/>
+      <x:c r="H34" s="129"/>
       <x:c r="I34" s="129"/>
       <x:c r="J34" s="129"/>
-      <x:c r="K34" s="106"/>
-      <x:c r="L34" s="107"/>
+      <x:c r="K34" s="129"/>
+      <x:c r="L34" s="232"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="112" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="128"/>
-      <x:c r="C35" s="68"/>
+      <x:c r="C35" s="128"/>
       <x:c r="D35" s="128"/>
       <x:c r="E35" s="128"/>
       <x:c r="F35" s="128"/>
       <x:c r="G35" s="120"/>
-      <x:c r="H35" s="68"/>
+      <x:c r="H35" s="128"/>
       <x:c r="I35" s="128"/>
       <x:c r="J35" s="128"/>
-      <x:c r="K35" s="68"/>
-      <x:c r="L35" s="69"/>
+      <x:c r="K35" s="128"/>
+      <x:c r="L35" s="231"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="113" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="129"/>
-      <x:c r="C36" s="106"/>
+      <x:c r="C36" s="129"/>
       <x:c r="D36" s="129"/>
       <x:c r="E36" s="129"/>
       <x:c r="F36" s="129"/>
       <x:c r="G36" s="121"/>
-      <x:c r="H36" s="106"/>
+      <x:c r="H36" s="129"/>
       <x:c r="I36" s="129"/>
       <x:c r="J36" s="129"/>
-      <x:c r="K36" s="106"/>
-      <x:c r="L36" s="107"/>
+      <x:c r="K36" s="129"/>
+      <x:c r="L36" s="232"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="112" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="128"/>
-      <x:c r="C37" s="68"/>
+      <x:c r="C37" s="128"/>
       <x:c r="D37" s="128"/>
       <x:c r="E37" s="128"/>
       <x:c r="F37" s="128"/>
       <x:c r="G37" s="120"/>
-      <x:c r="H37" s="68"/>
+      <x:c r="H37" s="128"/>
       <x:c r="I37" s="128"/>
       <x:c r="J37" s="128"/>
-      <x:c r="K37" s="68"/>
-      <x:c r="L37" s="69"/>
+      <x:c r="K37" s="128"/>
+      <x:c r="L37" s="231"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="113" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="129"/>
-      <x:c r="C38" s="106"/>
+      <x:c r="C38" s="129"/>
       <x:c r="D38" s="129"/>
       <x:c r="E38" s="129"/>
       <x:c r="F38" s="129"/>
       <x:c r="G38" s="121"/>
-      <x:c r="H38" s="106"/>
+      <x:c r="H38" s="129"/>
       <x:c r="I38" s="129"/>
       <x:c r="J38" s="129"/>
-      <x:c r="K38" s="106"/>
-      <x:c r="L38" s="107"/>
+      <x:c r="K38" s="129"/>
+      <x:c r="L38" s="232"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="112" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="128"/>
-      <x:c r="C39" s="68"/>
+      <x:c r="C39" s="128"/>
       <x:c r="D39" s="128"/>
       <x:c r="E39" s="128"/>
       <x:c r="F39" s="128"/>
       <x:c r="G39" s="120"/>
-      <x:c r="H39" s="68"/>
+      <x:c r="H39" s="128"/>
       <x:c r="I39" s="128"/>
       <x:c r="J39" s="128"/>
-      <x:c r="K39" s="68"/>
-      <x:c r="L39" s="69"/>
+      <x:c r="K39" s="128"/>
+      <x:c r="L39" s="231"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="113" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="129"/>
-      <x:c r="C40" s="106"/>
+      <x:c r="C40" s="129"/>
       <x:c r="D40" s="129"/>
       <x:c r="E40" s="129"/>
       <x:c r="F40" s="129"/>
       <x:c r="G40" s="121"/>
-      <x:c r="H40" s="106"/>
+      <x:c r="H40" s="129"/>
       <x:c r="I40" s="129"/>
       <x:c r="J40" s="129"/>
-      <x:c r="K40" s="106"/>
-      <x:c r="L40" s="107"/>
+      <x:c r="K40" s="129"/>
+      <x:c r="L40" s="232"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="112" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="128"/>
-      <x:c r="C41" s="68"/>
+      <x:c r="C41" s="128"/>
       <x:c r="D41" s="128"/>
       <x:c r="E41" s="128"/>
       <x:c r="F41" s="128"/>
       <x:c r="G41" s="120"/>
-      <x:c r="H41" s="68"/>
+      <x:c r="H41" s="128"/>
       <x:c r="I41" s="128"/>
       <x:c r="J41" s="128"/>
-      <x:c r="K41" s="68"/>
-      <x:c r="L41" s="69"/>
+      <x:c r="K41" s="128"/>
+      <x:c r="L41" s="231"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="113" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="129"/>
-      <x:c r="C42" s="106"/>
+      <x:c r="C42" s="129"/>
       <x:c r="D42" s="129"/>
       <x:c r="E42" s="129"/>
       <x:c r="F42" s="129"/>
       <x:c r="G42" s="121"/>
-      <x:c r="H42" s="106"/>
+      <x:c r="H42" s="129"/>
       <x:c r="I42" s="129"/>
       <x:c r="J42" s="129"/>
-      <x:c r="K42" s="106"/>
-      <x:c r="L42" s="107"/>
+      <x:c r="K42" s="129"/>
+      <x:c r="L42" s="232"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="112" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="128"/>
-      <x:c r="C43" s="68"/>
+      <x:c r="C43" s="128"/>
       <x:c r="D43" s="128"/>
       <x:c r="E43" s="128"/>
       <x:c r="F43" s="128"/>
       <x:c r="G43" s="120"/>
-      <x:c r="H43" s="68"/>
+      <x:c r="H43" s="128"/>
       <x:c r="I43" s="128"/>
       <x:c r="J43" s="128"/>
-      <x:c r="K43" s="68"/>
-      <x:c r="L43" s="69"/>
+      <x:c r="K43" s="128"/>
+      <x:c r="L43" s="231"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="113" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="129"/>
-      <x:c r="C44" s="106"/>
+      <x:c r="C44" s="129"/>
       <x:c r="D44" s="129"/>
       <x:c r="E44" s="129"/>
       <x:c r="F44" s="129"/>
       <x:c r="G44" s="121"/>
-      <x:c r="H44" s="106"/>
+      <x:c r="H44" s="129"/>
       <x:c r="I44" s="129"/>
       <x:c r="J44" s="129"/>
-      <x:c r="K44" s="106"/>
-      <x:c r="L44" s="107"/>
+      <x:c r="K44" s="129"/>
+      <x:c r="L44" s="232"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="112" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="128"/>
-      <x:c r="C45" s="68"/>
+      <x:c r="C45" s="128"/>
       <x:c r="D45" s="128"/>
       <x:c r="E45" s="128"/>
       <x:c r="F45" s="128"/>
       <x:c r="G45" s="120"/>
-      <x:c r="H45" s="68"/>
+      <x:c r="H45" s="128"/>
       <x:c r="I45" s="128"/>
       <x:c r="J45" s="128"/>
-      <x:c r="K45" s="68"/>
-      <x:c r="L45" s="69"/>
+      <x:c r="K45" s="128"/>
+      <x:c r="L45" s="231"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="113" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="129"/>
-      <x:c r="C46" s="106"/>
+      <x:c r="C46" s="129"/>
       <x:c r="D46" s="129"/>
       <x:c r="E46" s="129"/>
       <x:c r="F46" s="129"/>
       <x:c r="G46" s="121"/>
-      <x:c r="H46" s="106"/>
+      <x:c r="H46" s="129"/>
       <x:c r="I46" s="129"/>
       <x:c r="J46" s="129"/>
-      <x:c r="K46" s="106"/>
-      <x:c r="L46" s="107"/>
+      <x:c r="K46" s="129"/>
+      <x:c r="L46" s="232"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="112" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="128"/>
-      <x:c r="C47" s="68"/>
+      <x:c r="C47" s="128"/>
       <x:c r="D47" s="128"/>
       <x:c r="E47" s="128"/>
       <x:c r="F47" s="128"/>
       <x:c r="G47" s="120"/>
-      <x:c r="H47" s="68"/>
+      <x:c r="H47" s="128"/>
       <x:c r="I47" s="128"/>
       <x:c r="J47" s="128"/>
-      <x:c r="K47" s="68"/>
-      <x:c r="L47" s="69"/>
+      <x:c r="K47" s="128"/>
+      <x:c r="L47" s="231"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="113" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="129"/>
-      <x:c r="C48" s="106"/>
+      <x:c r="C48" s="129"/>
       <x:c r="D48" s="129"/>
       <x:c r="E48" s="129"/>
       <x:c r="F48" s="129"/>
       <x:c r="G48" s="121"/>
-      <x:c r="H48" s="106"/>
+      <x:c r="H48" s="129"/>
       <x:c r="I48" s="129"/>
       <x:c r="J48" s="129"/>
-      <x:c r="K48" s="106"/>
-      <x:c r="L48" s="107"/>
+      <x:c r="K48" s="129"/>
+      <x:c r="L48" s="232"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="112" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="128"/>
-      <x:c r="C49" s="68"/>
+      <x:c r="C49" s="128"/>
       <x:c r="D49" s="128"/>
       <x:c r="E49" s="128"/>
       <x:c r="F49" s="128"/>
       <x:c r="G49" s="120"/>
-      <x:c r="H49" s="68"/>
+      <x:c r="H49" s="128"/>
       <x:c r="I49" s="128"/>
       <x:c r="J49" s="128"/>
-      <x:c r="K49" s="68"/>
-      <x:c r="L49" s="69"/>
+      <x:c r="K49" s="128"/>
+      <x:c r="L49" s="231"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="113" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="129"/>
-      <x:c r="C50" s="106"/>
+      <x:c r="C50" s="129"/>
       <x:c r="D50" s="129"/>
       <x:c r="E50" s="129"/>
       <x:c r="F50" s="129"/>
       <x:c r="G50" s="121"/>
-      <x:c r="H50" s="106"/>
+      <x:c r="H50" s="129"/>
       <x:c r="I50" s="129"/>
       <x:c r="J50" s="129"/>
-      <x:c r="K50" s="106"/>
-      <x:c r="L50" s="107"/>
+      <x:c r="K50" s="129"/>
+      <x:c r="L50" s="232"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="112" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="128"/>
-      <x:c r="C51" s="68"/>
+      <x:c r="C51" s="128"/>
       <x:c r="D51" s="128"/>
       <x:c r="E51" s="128"/>
       <x:c r="F51" s="128"/>
       <x:c r="G51" s="120"/>
-      <x:c r="H51" s="68"/>
+      <x:c r="H51" s="128"/>
       <x:c r="I51" s="128"/>
       <x:c r="J51" s="128"/>
-      <x:c r="K51" s="68"/>
-      <x:c r="L51" s="69"/>
+      <x:c r="K51" s="128"/>
+      <x:c r="L51" s="231"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="113" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="129"/>
-      <x:c r="C52" s="106"/>
+      <x:c r="C52" s="129"/>
       <x:c r="D52" s="129"/>
       <x:c r="E52" s="129"/>
       <x:c r="F52" s="129"/>
       <x:c r="G52" s="121"/>
-      <x:c r="H52" s="106"/>
+      <x:c r="H52" s="129"/>
       <x:c r="I52" s="129"/>
       <x:c r="J52" s="129"/>
-      <x:c r="K52" s="106"/>
-      <x:c r="L52" s="107"/>
+      <x:c r="K52" s="129"/>
+      <x:c r="L52" s="232"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="114" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="130"/>
-      <x:c r="C53" s="71"/>
+      <x:c r="C53" s="130"/>
       <x:c r="D53" s="130"/>
       <x:c r="E53" s="130"/>
       <x:c r="F53" s="130"/>
       <x:c r="G53" s="122"/>
-      <x:c r="H53" s="71"/>
+      <x:c r="H53" s="130"/>
       <x:c r="I53" s="130"/>
       <x:c r="J53" s="130"/>
-      <x:c r="K53" s="71"/>
-      <x:c r="L53" s="72"/>
+      <x:c r="K53" s="130"/>
+      <x:c r="L53" s="233"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1972,37 +2002,37 @@
       <x:c r="A4" s="169" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="170" t="str">
+      <x:c r="B4" s="234" t="str">
         <x:v>SV26001</x:v>
       </x:c>
-      <x:c r="C4" s="170" t="str">
+      <x:c r="C4" s="234" t="str">
         <x:v>Nguyễn Văn A</x:v>
       </x:c>
-      <x:c r="D4" s="170" t="str">
+      <x:c r="D4" s="234" t="str">
         <x:v>sv26001@gmail.com</x:v>
       </x:c>
-      <x:c r="E4" s="170" t="str">
+      <x:c r="E4" s="234" t="str">
         <x:v>123456</x:v>
       </x:c>
-      <x:c r="F4" s="170" t="str">
+      <x:c r="F4" s="234" t="str">
         <x:v>CDTH26A</x:v>
       </x:c>
-      <x:c r="G4" s="170" t="str">
+      <x:c r="G4" s="236" t="str">
         <x:v>01/01/2006</x:v>
       </x:c>
-      <x:c r="H4" s="170" t="str">
+      <x:c r="H4" s="234" t="str">
         <x:v>Nam</x:v>
       </x:c>
-      <x:c r="I4" s="170" t="str">
+      <x:c r="I4" s="234" t="str">
         <x:v>0900000001</x:v>
       </x:c>
-      <x:c r="J4" s="170" t="str">
+      <x:c r="J4" s="234" t="str">
         <x:v>012345678901</x:v>
       </x:c>
-      <x:c r="K4" s="170" t="str">
+      <x:c r="K4" s="234" t="str">
         <x:v>Cần Thơ</x:v>
       </x:c>
-      <x:c r="L4" s="171" t="str">
+      <x:c r="L4" s="235" t="str">
         <x:v>Đang học</x:v>
       </x:c>
     </x:row>
@@ -2023,15 +2053,20 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="181" t="str">
+      <x:c r="A1" s="237" t="str">
         <x:v>MẪU NHẬP SINH VIÊN - HƯỚNG DẪN</x:v>
       </x:c>
+      <x:c r="B1" s="59"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="59"/>
+      <x:c r="B2" s="59"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="189" t="str">
+      <x:c r="A3" s="238" t="str">
         <x:v>Nội dung</x:v>
       </x:c>
-      <x:c r="B3" s="190" t="str">
+      <x:c r="B3" s="239" t="str">
         <x:v>Chi tiết</x:v>
       </x:c>
     </x:row>
@@ -2122,6 +2157,34 @@
       <x:c r="B14" s="202" t="str">
         <x:v>Email, Mã sinh viên và CCCD không được trùng trong file hoặc CSDL.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="59" t="str">
+        <x:v>Định dạng ô</x:v>
+      </x:c>
+      <x:c r="B15" s="59" t="str">
+        <x:v>Mã SV, Mật khẩu, SĐT và CCCD được định dạng Văn bản để giữ số 0 đầu.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="59"/>
+      <x:c r="B16" s="59"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="59"/>
+      <x:c r="B17" s="59"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="59"/>
+      <x:c r="B18" s="59"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="59"/>
+      <x:c r="B19" s="59"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="59"/>
+      <x:c r="B20" s="59"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
